--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/7722-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/7722-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\20260215_1_2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B55502A2-D3E7-4171-BF82-1C68751DCE26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C224A127-3D22-4CE4-B793-6449E633EAF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="1500" windowWidth="21600" windowHeight="11295" xr2:uid="{2CDD959D-8489-49A3-ACF2-9659FE499FA3}"/>
+    <workbookView xWindow="3855" yWindow="285" windowWidth="21600" windowHeight="13080" xr2:uid="{CC931859-252F-45E1-85EC-39A5B9000AE3}"/>
   </bookViews>
   <sheets>
     <sheet name="7722-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -20,24 +20,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>股利</t>
   </si>
   <si>
+    <t>所屬</t>
+  </si>
+  <si>
+    <t>期間</t>
+  </si>
+  <si>
     <t>發放</t>
   </si>
   <si>
-    <t>期間</t>
-  </si>
-  <si>
-    <t>所屬</t>
-  </si>
-  <si>
     <t>股利政策</t>
   </si>
   <si>
-    <t>現金殖利率</t>
+    <t>現金+股票殖利率</t>
   </si>
   <si>
     <t>股東股利 (元/股)</t>
@@ -70,7 +70,7 @@
     <t>年度</t>
   </si>
   <si>
-    <t>除息前</t>
+    <t>除權/息前</t>
   </si>
   <si>
     <t>年均價</t>
@@ -91,13 +91,25 @@
     <t>公積</t>
   </si>
   <si>
+    <t>除息</t>
+  </si>
+  <si>
+    <t>除權</t>
+  </si>
+  <si>
+    <t>利率</t>
+  </si>
+  <si>
     <t>價格</t>
   </si>
   <si>
-    <t>利率</t>
+    <t> '25/09/04 </t>
   </si>
   <si>
     <t>-</t>
+  </si>
+  <si>
+    <t> 無 </t>
   </si>
   <si>
     <t>累計</t>
@@ -1396,18 +1408,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2388C2B-CA41-4CDF-BBC4-AE9DFA7895FE}">
-  <dimension ref="A1:W7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E0B8808-DAFC-43A0-80BB-D9B8FF759125}">
+  <dimension ref="A1:X7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.25" customWidth="1"/>
-    <col min="3" max="17" width="6.75" customWidth="1"/>
-    <col min="18" max="18" width="7.125" customWidth="1"/>
-    <col min="19" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="8.375" customWidth="1"/>
+    <col min="1" max="2" width="11.375" customWidth="1"/>
+    <col min="3" max="3" width="10.25" customWidth="1"/>
+    <col min="4" max="18" width="6.25" customWidth="1"/>
+    <col min="19" max="19" width="6.625" customWidth="1"/>
+    <col min="20" max="23" width="6.25" customWidth="1"/>
+    <col min="24" max="24" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -1438,9 +1451,10 @@
       <c r="T1" s="25"/>
       <c r="U1" s="25"/>
       <c r="V1" s="25"/>
-      <c r="W1" s="17"/>
+      <c r="W1" s="25"/>
+      <c r="X1" s="17"/>
     </row>
-    <row r="2" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
@@ -1473,9 +1487,10 @@
       <c r="T2" s="27"/>
       <c r="U2" s="27"/>
       <c r="V2" s="27"/>
-      <c r="W2" s="28"/>
+      <c r="W2" s="27"/>
+      <c r="X2" s="28"/>
     </row>
-    <row r="3" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
         <v>2</v>
       </c>
@@ -1508,25 +1523,26 @@
       <c r="N3" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="31"/>
-      <c r="P3" s="29" t="s">
+      <c r="O3" s="30"/>
+      <c r="P3" s="31"/>
+      <c r="Q3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="Q3" s="31"/>
-      <c r="R3" s="29" t="s">
+      <c r="R3" s="31"/>
+      <c r="S3" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="S3" s="31"/>
-      <c r="T3" s="29" t="s">
+      <c r="T3" s="31"/>
+      <c r="U3" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="U3" s="31"/>
-      <c r="V3" s="29" t="s">
+      <c r="V3" s="31"/>
+      <c r="W3" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="W3" s="31"/>
+      <c r="X3" s="31"/>
     </row>
-    <row r="4" spans="1:23" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="20"/>
       <c r="B4" s="21"/>
       <c r="C4" s="6"/>
@@ -1567,37 +1583,40 @@
         <v>24</v>
       </c>
       <c r="P4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="Q4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="R4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="S4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="T4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="U4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V4" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="W4" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="X4" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="32">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="B5" s="33"/>
-      <c r="C5" s="9">
-        <v>2024</v>
+      <c r="C5" s="9" t="s">
+        <v>27</v>
       </c>
       <c r="D5" s="10">
         <v>1.5</v>
@@ -1624,7 +1643,7 @@
         <v>1</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M5" s="9">
         <v>2025</v>
@@ -1632,41 +1651,44 @@
       <c r="N5" s="11">
         <v>600</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="10">
         <v>0.25</v>
       </c>
-      <c r="P5" s="11">
+      <c r="Q5" s="11">
         <v>638</v>
       </c>
-      <c r="Q5" s="10">
+      <c r="R5" s="10">
         <v>0.24</v>
       </c>
-      <c r="R5" s="11">
+      <c r="S5" s="11">
         <v>570</v>
       </c>
-      <c r="S5" s="10">
+      <c r="T5" s="10">
         <v>0.26</v>
       </c>
-      <c r="T5" s="11">
+      <c r="U5" s="11">
         <v>934</v>
       </c>
-      <c r="U5" s="10">
+      <c r="V5" s="10">
         <v>0.16</v>
       </c>
-      <c r="V5" s="11">
+      <c r="W5" s="11">
         <v>460</v>
       </c>
-      <c r="W5" s="10">
+      <c r="X5" s="10">
         <v>0.33</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="12" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="12" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="34">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B6" s="35"/>
-      <c r="C6" s="13">
-        <v>2023</v>
+      <c r="C6" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="D6" s="14">
         <v>0</v>
@@ -1690,48 +1712,51 @@
         <v>0</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L6" s="14" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M6" s="13">
         <v>2024</v>
       </c>
       <c r="N6" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="O6" s="14">
-        <v>0</v>
-      </c>
-      <c r="P6" s="15">
+        <v>28</v>
+      </c>
+      <c r="O6" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="15">
         <v>468</v>
       </c>
-      <c r="Q6" s="14">
-        <v>0</v>
-      </c>
-      <c r="R6" s="15">
+      <c r="R6" s="14">
+        <v>0</v>
+      </c>
+      <c r="S6" s="15">
         <v>459.5</v>
       </c>
-      <c r="S6" s="14">
-        <v>0</v>
-      </c>
-      <c r="T6" s="15">
+      <c r="T6" s="14">
+        <v>0</v>
+      </c>
+      <c r="U6" s="15">
         <v>520</v>
       </c>
-      <c r="U6" s="14">
-        <v>0</v>
-      </c>
-      <c r="V6" s="15">
+      <c r="V6" s="14">
+        <v>0</v>
+      </c>
+      <c r="W6" s="15">
         <v>426</v>
       </c>
-      <c r="W6" s="14">
+      <c r="X6" s="14">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:23" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="8" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B7" s="33"/>
       <c r="C7" s="10"/>
@@ -1769,14 +1794,15 @@
       <c r="U7" s="10"/>
       <c r="V7" s="10"/>
       <c r="W7" s="10"/>
+      <c r="X7" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="P3:Q3"/>
-    <mergeCell ref="R3:S3"/>
-    <mergeCell ref="T3:U3"/>
-    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="U3:V3"/>
+    <mergeCell ref="W3:X3"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A1:B1"/>
@@ -1784,11 +1810,11 @@
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D1:L1"/>
-    <mergeCell ref="M1:W2"/>
+    <mergeCell ref="M1:X2"/>
     <mergeCell ref="D2:J2"/>
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
-    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="N3:P3"/>
   </mergeCells>
   <phoneticPr fontId="22" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
